--- a/Data/FlightPlan/FPL_29SEP26.xlsx
+++ b/Data/FlightPlan/FPL_29SEP26.xlsx
@@ -245,7 +245,7 @@
     <t>08:45</t>
   </si>
   <si>
-    <t>10:53</t>
+    <t>11:01</t>
   </si>
   <si>
     <t>15:30</t>
@@ -374,6 +374,9 @@
     <t>09:00</t>
   </si>
   <si>
+    <t>10:33</t>
+  </si>
+  <si>
     <t>10:50</t>
   </si>
   <si>
@@ -401,6 +404,9 @@
     <t>13:35</t>
   </si>
   <si>
+    <t>14:00</t>
+  </si>
+  <si>
     <t>14:35</t>
   </si>
   <si>
@@ -488,717 +494,744 @@
     <t>10:15</t>
   </si>
   <si>
+    <t>10:13</t>
+  </si>
+  <si>
     <t>12:10</t>
   </si>
   <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>13:17</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>09:26</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>08:02</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>13:59</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>10:49</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>NOZ</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>14:06</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>09:54</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>11:38</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:43</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>06:53</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>08:36</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>09:09</t>
+  </si>
+  <si>
+    <t>11:44</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>09:02</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>431A *</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>11:03</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>05:31</t>
+  </si>
+  <si>
+    <t>401A</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>09:29</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>07:44</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>09:19</t>
+  </si>
+  <si>
+    <t>11:22</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>06:27</t>
+  </si>
+  <si>
+    <t>10:09</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>12:04</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>09:56</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>13:43</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>07:57</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>08:38</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>06:47</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>06:38</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>VN-A674</t>
+  </si>
+  <si>
+    <t>11:57</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>10:59</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>10:22</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>10:18</t>
+  </si>
+  <si>
     <t>1382A *</t>
   </si>
   <si>
     <t>15:20</t>
   </si>
   <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>13:17</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>HYD</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>09:26</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>08:02</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>13:59</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>NOZ</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>09:54</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>11:38</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:43</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>06:53</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>08:36</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>09:09</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>09:02</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>431A *</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>05:31</t>
-  </si>
-  <si>
-    <t>401A</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>09:29</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>07:44</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>09:19</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>06:27</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>12:04</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>09:56</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>13:43</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>07:57</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>08:38</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>06:47</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>06:38</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>VN-A674</t>
-  </si>
-  <si>
-    <t>11:57</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>10:22</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>10:18</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
     <t>VN-A684</t>
   </si>
   <si>
@@ -1214,6 +1247,9 @@
     <t>VN-A685</t>
   </si>
   <si>
+    <t>14:01</t>
+  </si>
+  <si>
     <t>VN-A693</t>
   </si>
   <si>
@@ -1241,7 +1277,7 @@
     <t>08:05</t>
   </si>
   <si>
-    <t>10:19</t>
+    <t>15:00</t>
   </si>
   <si>
     <t>VN-A811</t>
@@ -1283,7 +1319,7 @@
     <t>VN-A820</t>
   </si>
   <si>
-    <t>10:27</t>
+    <t>10:47</t>
   </si>
   <si>
     <t>SYD</t>
@@ -1292,7 +1328,7 @@
     <t>Total Record(s): 351</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 29, 2026 08:54</t>
+    <t xml:space="preserve">Generated on  Sep 29, 2026 09:39</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3398,7 +3434,9 @@
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
-      <c r="M57" s="7"/>
+      <c t="s" r="M57" s="7">
+        <v>121</v>
+      </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c t="s" r="A58" s="6">
@@ -3424,10 +3462,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3457,10 +3495,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3490,10 +3528,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3526,7 +3564,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3535,17 +3573,19 @@
         <v>27</v>
       </c>
       <c t="s" r="H62" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="I62" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
+      <c t="s" r="M62" s="7">
+        <v>131</v>
+      </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c t="s" r="A63" s="6">
@@ -3559,22 +3599,22 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="H63" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3592,7 +3632,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3601,13 +3641,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H64" s="8">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c t="s" r="I64" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3625,19 +3665,19 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c t="s" r="H65" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c t="s" r="J65" s="7">
         <v>20</v>
@@ -3673,19 +3713,19 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G67" s="8">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="H67" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c t="s" r="J67" s="7">
         <v>106</v>
@@ -3693,7 +3733,7 @@
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c t="s" r="M67" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -3708,7 +3748,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3720,10 +3760,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3741,7 +3781,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3774,7 +3814,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3786,10 +3826,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3807,7 +3847,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3819,10 +3859,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3840,7 +3880,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3852,7 +3892,7 @@
         <v>113</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J72" s="7">
         <v>85</v>
@@ -3888,7 +3928,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3897,13 +3937,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3921,19 +3961,19 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J75" s="7">
         <v>61</v>
@@ -3954,7 +3994,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -3966,10 +4006,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3987,7 +4027,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -3999,10 +4039,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -4020,7 +4060,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4032,10 +4072,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4068,7 +4108,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4077,17 +4117,19 @@
         <v>27</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I80" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
-      <c r="M80" s="7"/>
+      <c t="s" r="M80" s="7">
+        <v>161</v>
+      </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c t="s" r="A81" s="6">
@@ -4101,22 +4143,22 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4126,15 +4168,15 @@
       <c t="s" r="A82" s="6">
         <v>13</v>
       </c>
-      <c t="s" r="B82" s="7">
-        <v>160</v>
+      <c r="B82" s="7">
+        <v>252</v>
       </c>
       <c t="s" r="C82" s="7">
         <v>14</v>
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4143,50 +4185,46 @@
         <v>27</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>59</v>
-      </c>
-      <c t="s" r="K82" s="7">
-        <v>129</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="K82" s="7"/>
       <c r="L82" s="7"/>
-      <c t="s" r="M82" s="7">
-        <v>59</v>
-      </c>
+      <c r="M82" s="7"/>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c t="s" r="A83" s="6">
         <v>13</v>
       </c>
       <c r="B83" s="7">
-        <v>1383</v>
+        <v>253</v>
       </c>
       <c t="s" r="C83" s="7">
         <v>14</v>
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4197,14 +4235,14 @@
         <v>13</v>
       </c>
       <c r="B84" s="7">
-        <v>282</v>
+        <v>216</v>
       </c>
       <c t="s" r="C84" s="7">
         <v>14</v>
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4213,13 +4251,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4230,29 +4268,29 @@
         <v>13</v>
       </c>
       <c r="B85" s="7">
-        <v>283</v>
+        <v>217</v>
       </c>
       <c t="s" r="C85" s="7">
         <v>14</v>
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4285,7 +4323,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4294,18 +4332,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4320,22 +4358,22 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="H88" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4353,7 +4391,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4362,13 +4400,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4386,22 +4424,22 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c t="s" r="H90" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4434,7 +4472,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4446,10 +4484,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4469,7 +4507,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4478,18 +4516,18 @@
         <v>55</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c t="s" r="I93" s="7">
         <v>85</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -4504,13 +4542,13 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>27</v>
@@ -4519,7 +4557,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4537,7 +4575,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4570,7 +4608,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4582,7 +4620,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>116</v>
@@ -4603,7 +4641,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4615,10 +4653,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4636,7 +4674,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4648,10 +4686,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4684,7 +4722,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4696,7 +4734,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="J100" s="7">
         <v>38</v>
@@ -4704,7 +4742,7 @@
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c t="s" r="M100" s="7">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -4719,7 +4757,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4738,7 +4776,9 @@
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
-      <c r="M101" s="7"/>
+      <c t="s" r="M101" s="7">
+        <v>39</v>
+      </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
       <c t="s" r="A102" s="6">
@@ -4752,7 +4792,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4764,7 +4804,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>89</v>
@@ -4785,7 +4825,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4797,10 +4837,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4818,7 +4858,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4833,7 +4873,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4851,7 +4891,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4884,7 +4924,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4899,7 +4939,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4917,7 +4957,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4929,10 +4969,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4965,7 +5005,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4977,15 +5017,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c t="s" r="M109" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -5000,7 +5040,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5012,10 +5052,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5033,7 +5073,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5045,7 +5085,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J111" s="7">
         <v>98</v>
@@ -5081,22 +5121,22 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5116,7 +5156,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5125,7 +5165,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="I114" s="7">
         <v>23</v>
@@ -5149,22 +5189,22 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5182,7 +5222,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5194,10 +5234,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5230,7 +5270,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5239,10 +5279,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>107</v>
@@ -5250,7 +5290,7 @@
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5265,13 +5305,13 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>34</v>
@@ -5280,7 +5320,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5298,7 +5338,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5307,13 +5347,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5331,22 +5371,22 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5379,13 +5419,13 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>27</v>
@@ -5394,7 +5434,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5414,7 +5454,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5426,10 +5466,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5447,7 +5487,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5462,7 +5502,7 @@
         <v>95</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5495,7 +5535,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5507,7 +5547,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>22</v>
@@ -5530,7 +5570,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5542,14 +5582,16 @@
         <v>34</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>88</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
-      <c r="M128" s="7"/>
+      <c t="s" r="M128" s="7">
+        <v>220</v>
+      </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
       <c t="s" r="A129" s="6">
@@ -5563,7 +5605,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5575,10 +5617,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5596,7 +5638,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5608,10 +5650,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5629,7 +5671,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5638,13 +5680,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5662,13 +5704,13 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>34</v>
@@ -5710,7 +5752,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5722,10 +5764,10 @@
         <v>90</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5739,11 +5781,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C135" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5772,11 +5814,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C136" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5785,7 +5827,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c t="s" r="I136" s="7">
         <v>80</v>
@@ -5805,23 +5847,23 @@
         <v>5069</v>
       </c>
       <c t="s" r="C137" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c t="s" r="J137" s="7">
         <v>65</v>
@@ -5857,7 +5899,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5872,11 +5914,13 @@
         <v>56</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
-      <c r="M139" s="7"/>
+      <c t="s" r="M139" s="7">
+        <v>230</v>
+      </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c t="s" r="A140" s="6">
@@ -5886,11 +5930,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5905,7 +5949,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5919,11 +5963,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5932,13 +5976,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5971,7 +6015,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5983,15 +6027,15 @@
         <v>90</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6006,7 +6050,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6054,7 +6098,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6066,17 +6110,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="K146" s="7">
         <v>85</v>
       </c>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6091,7 +6135,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6100,13 +6144,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6124,19 +6168,19 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c t="s" r="J148" s="7">
         <v>117</v>
@@ -6157,7 +6201,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6169,10 +6213,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>239</v>
+        <v>169</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6205,7 +6249,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6214,10 +6258,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>107</v>
@@ -6238,13 +6282,13 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="H152" s="8">
         <v>27</v>
@@ -6253,7 +6297,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6271,7 +6315,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6280,13 +6324,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6319,7 +6363,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6331,10 +6375,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6354,7 +6398,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6363,13 +6407,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6387,22 +6431,22 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6420,7 +6464,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6432,10 +6476,10 @@
         <v>113</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6468,7 +6512,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6477,10 +6521,10 @@
         <v>90</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>80</v>
@@ -6501,22 +6545,22 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>90</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6534,7 +6578,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6549,7 +6593,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6582,7 +6626,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6594,15 +6638,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -6617,7 +6661,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6626,13 +6670,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6650,13 +6694,13 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>27</v>
@@ -6683,22 +6727,22 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
+        <v>255</v>
+      </c>
+      <c r="F167" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G167" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H167" s="8">
+        <v>260</v>
+      </c>
+      <c t="s" r="I167" s="7">
         <v>251</v>
       </c>
-      <c r="F167" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G167" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H167" s="8">
-        <v>256</v>
-      </c>
-      <c t="s" r="I167" s="7">
-        <v>247</v>
-      </c>
       <c t="s" r="J167" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6716,22 +6760,22 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6764,7 +6808,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6773,10 +6817,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>37</v>
@@ -6784,7 +6828,7 @@
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -6799,19 +6843,19 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>22</v>
@@ -6819,7 +6863,7 @@
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -6834,7 +6878,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6843,10 +6887,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>23</v>
@@ -6867,13 +6911,13 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>27</v>
@@ -6900,7 +6944,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6909,7 +6953,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c t="s" r="I174" s="7">
         <v>115</v>
@@ -6933,13 +6977,13 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>27</v>
@@ -6948,7 +6992,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6966,7 +7010,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6978,10 +7022,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7014,7 +7058,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7026,15 +7070,15 @@
         <v>60</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7049,7 +7093,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7068,7 +7112,9 @@
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
-      <c r="M179" s="7"/>
+      <c t="s" r="M179" s="7">
+        <v>274</v>
+      </c>
     </row>
     <row r="180" ht="15" customHeight="1">
       <c t="s" r="A180" s="6">
@@ -7082,7 +7128,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7094,7 +7140,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>23</v>
@@ -7115,7 +7161,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7127,7 +7173,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>92</v>
@@ -7148,7 +7194,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7160,7 +7206,7 @@
         <v>90</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>62</v>
@@ -7196,7 +7242,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7208,10 +7254,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7229,7 +7275,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7241,7 +7287,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>107</v>
@@ -7262,7 +7308,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7271,13 +7317,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>273</v>
+        <v>164</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7295,22 +7341,22 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7328,7 +7374,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7337,13 +7383,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7361,22 +7407,22 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7409,7 +7455,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7444,7 +7490,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7456,7 +7502,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>22</v>
@@ -7464,7 +7510,7 @@
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -7479,7 +7525,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7488,17 +7534,19 @@
         <v>34</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
-      <c r="M193" s="7"/>
+      <c t="s" r="M193" s="7">
+        <v>88</v>
+      </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
       <c t="s" r="A194" s="6">
@@ -7512,19 +7560,19 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>106</v>
@@ -7538,14 +7586,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B195" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c t="s" r="C195" s="7">
         <v>14</v>
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7582,7 +7630,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7597,7 +7645,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7615,7 +7663,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7630,7 +7678,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7648,7 +7696,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7660,10 +7708,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7696,7 +7744,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7731,7 +7779,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7743,14 +7791,16 @@
         <v>94</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c t="s" r="J201" s="7">
         <v>42</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
-      <c r="M201" s="7"/>
+      <c t="s" r="M201" s="7">
+        <v>291</v>
+      </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
       <c t="s" r="A202" s="6">
@@ -7764,7 +7814,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7773,13 +7823,13 @@
         <v>94</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7797,13 +7847,13 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>94</v>
@@ -7830,7 +7880,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7839,7 +7889,7 @@
         <v>94</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c t="s" r="I204" s="7">
         <v>110</v>
@@ -7863,22 +7913,22 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>94</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7896,7 +7946,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7908,10 +7958,10 @@
         <v>87</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7944,7 +7994,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7956,15 +8006,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -7979,7 +8029,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7988,7 +8038,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="I209" s="7">
         <v>114</v>
@@ -7998,7 +8048,9 @@
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
-      <c r="M209" s="7"/>
+      <c t="s" r="M209" s="7">
+        <v>57</v>
+      </c>
     </row>
     <row r="210" ht="15" customHeight="1">
       <c t="s" r="A210" s="6">
@@ -8012,22 +8064,22 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -8045,7 +8097,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8054,7 +8106,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c t="s" r="I211" s="7">
         <v>92</v>
@@ -8078,13 +8130,13 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>27</v>
@@ -8119,14 +8171,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B214" s="7">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8135,20 +8187,20 @@
         <v>34</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c t="s" r="K214" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8163,19 +8215,19 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>114</v>
@@ -8198,22 +8250,22 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="I216" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8231,19 +8283,19 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>92</v>
@@ -8264,7 +8316,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8297,7 +8349,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8312,7 +8364,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8345,7 +8397,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8357,17 +8409,17 @@
         <v>94</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>22</v>
       </c>
       <c t="s" r="K221" s="7">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -8382,7 +8434,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8397,7 +8449,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8415,7 +8467,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8424,10 +8476,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>59</v>
@@ -8448,19 +8500,19 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>93</v>
@@ -8481,7 +8533,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8490,13 +8542,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8514,22 +8566,22 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8562,7 +8614,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8571,13 +8623,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8595,19 +8647,19 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>44</v>
@@ -8628,7 +8680,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8640,10 +8692,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8661,7 +8713,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8673,10 +8725,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8709,7 +8761,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8718,18 +8770,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -8744,19 +8796,19 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>114</v>
@@ -8764,7 +8816,7 @@
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -8779,7 +8831,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8794,11 +8846,13 @@
         <v>54</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
-      <c r="M235" s="7"/>
+      <c t="s" r="M235" s="7">
+        <v>315</v>
+      </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
       <c t="s" r="A236" s="6">
@@ -8812,7 +8866,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8824,7 +8878,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>107</v>
@@ -8845,7 +8899,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8854,13 +8908,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8878,22 +8932,22 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8911,7 +8965,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8923,10 +8977,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8959,7 +9013,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8971,15 +9025,15 @@
         <v>34</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -8994,7 +9048,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9006,10 +9060,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9027,7 +9081,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9039,7 +9093,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>273</v>
+        <v>164</v>
       </c>
       <c t="s" r="J243" s="7">
         <v>95</v>
@@ -9060,7 +9114,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9075,7 +9129,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9108,7 +9162,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9117,18 +9171,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c t="s" r="I246" s="7">
         <v>35</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9143,19 +9197,19 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>77</v>
@@ -9163,7 +9217,7 @@
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9178,7 +9232,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9190,14 +9244,16 @@
         <v>27</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>39</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
-      <c r="M248" s="7"/>
+      <c t="s" r="M248" s="7">
+        <v>326</v>
+      </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
       <c t="s" r="A249" s="6">
@@ -9211,7 +9267,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9244,7 +9300,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9256,10 +9312,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9277,7 +9333,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9289,10 +9345,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9310,7 +9366,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9322,10 +9378,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9343,7 +9399,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9352,13 +9408,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9376,22 +9432,22 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9424,7 +9480,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9433,10 +9489,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>67</v>
@@ -9444,7 +9500,7 @@
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -9459,22 +9515,22 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9492,7 +9548,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9501,13 +9557,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>162</v>
+        <v>336</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9525,22 +9581,22 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9569,11 +9625,11 @@
         <v>8520</v>
       </c>
       <c t="s" r="C261" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9582,10 +9638,10 @@
         <v>94</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>61</v>
@@ -9602,26 +9658,26 @@
         <v>8521</v>
       </c>
       <c t="s" r="C262" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>94</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9639,7 +9695,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9651,10 +9707,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9687,7 +9743,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9699,10 +9755,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>162</v>
+        <v>336</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9720,7 +9776,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9732,10 +9788,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9768,7 +9824,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -9780,7 +9836,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>114</v>
@@ -9788,7 +9844,7 @@
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -9803,7 +9859,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -9818,7 +9874,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9836,7 +9892,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -9848,7 +9904,7 @@
         <v>108</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>92</v>
@@ -9869,7 +9925,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
@@ -9881,10 +9937,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9902,7 +9958,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -9911,13 +9967,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c t="s" r="I272" s="7">
         <v>110</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9935,22 +9991,22 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9983,7 +10039,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9992,13 +10048,13 @@
         <v>94</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="I275" s="7">
         <v>39</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -10016,22 +10072,22 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>94</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10049,7 +10105,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10061,10 +10117,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10082,7 +10138,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10094,7 +10150,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>162</v>
+        <v>336</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>110</v>
@@ -10115,7 +10171,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10127,10 +10183,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10163,27 +10219,27 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10191,14 +10247,14 @@
         <v>13</v>
       </c>
       <c r="B282" s="7">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c t="s" r="C282" s="7">
         <v>14</v>
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10207,13 +10263,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>108</v>
+        <v>269</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>273</v>
+        <v>322</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10224,29 +10280,29 @@
         <v>13</v>
       </c>
       <c r="B283" s="7">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c t="s" r="C283" s="7">
         <v>14</v>
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>108</v>
+        <v>269</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>95</v>
+        <v>243</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10264,7 +10320,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10273,13 +10329,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10297,22 +10353,22 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10345,7 +10401,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10354,10 +10410,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>38</v>
@@ -10365,7 +10421,7 @@
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10380,27 +10436,27 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10415,7 +10471,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10430,7 +10486,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>350</v>
+        <v>163</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10448,7 +10504,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10460,7 +10516,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>45</v>
@@ -10481,7 +10537,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10493,7 +10549,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>96</v>
@@ -10529,7 +10585,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10544,10 +10600,10 @@
         <v>35</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c t="s" r="K293" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
@@ -10566,7 +10622,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10578,17 +10634,17 @@
         <v>27</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="K294" s="7">
         <v>56</v>
       </c>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -10603,7 +10659,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10612,13 +10668,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10636,13 +10692,13 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>27</v>
@@ -10651,7 +10707,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10669,7 +10725,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10678,13 +10734,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c t="s" r="I297" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10702,22 +10758,22 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10750,7 +10806,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -10759,17 +10815,19 @@
         <v>27</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>120</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
-      <c r="M300" s="7"/>
+      <c t="s" r="M300" s="7">
+        <v>201</v>
+      </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
       <c t="s" r="A301" s="6">
@@ -10783,13 +10841,13 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>17</v>
@@ -10798,7 +10856,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10816,7 +10874,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10825,13 +10883,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10849,22 +10907,22 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10882,7 +10940,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10891,13 +10949,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10915,22 +10973,22 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10963,7 +11021,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -10978,7 +11036,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10996,7 +11054,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11008,10 +11066,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -11029,7 +11087,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11038,13 +11096,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -11062,19 +11120,19 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>117</v>
@@ -11110,7 +11168,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11119,7 +11177,7 @@
         <v>34</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c t="s" r="I312" s="7">
         <v>36</v>
@@ -11130,7 +11188,7 @@
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11145,26 +11203,28 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
-      <c r="M313" s="7"/>
+      <c t="s" r="M313" s="7">
+        <v>88</v>
+      </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
       <c t="s" r="A314" s="6">
@@ -11178,7 +11238,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11190,10 +11250,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11211,7 +11271,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11223,10 +11283,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11244,7 +11304,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11256,10 +11316,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11277,7 +11337,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11289,10 +11349,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11325,7 +11385,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11334,18 +11394,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -11360,13 +11420,13 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>27</v>
@@ -11375,7 +11435,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11393,7 +11453,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11402,10 +11462,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>50</v>
@@ -11426,19 +11486,19 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>35</v>
@@ -11474,7 +11534,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11489,11 +11549,13 @@
         <v>120</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
-      <c r="M324" s="7"/>
+      <c t="s" r="M324" s="7">
+        <v>377</v>
+      </c>
     </row>
     <row r="325" ht="15" customHeight="1">
       <c t="s" r="A325" s="6">
@@ -11507,7 +11569,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11540,7 +11602,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -11549,10 +11611,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>79</v>
@@ -11573,22 +11635,22 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11606,7 +11668,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11618,10 +11680,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11639,7 +11701,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11654,7 +11716,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11687,7 +11749,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11699,7 +11761,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>102</v>
@@ -11707,7 +11769,7 @@
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>370</v>
+        <v>379</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -11722,7 +11784,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11731,17 +11793,19 @@
         <v>27</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
-      <c r="M332" s="7"/>
+      <c t="s" r="M332" s="7">
+        <v>56</v>
+      </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
       <c t="s" r="A333" s="6">
@@ -11755,13 +11819,13 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>27</v>
@@ -11770,7 +11834,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11788,7 +11852,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11800,10 +11864,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11821,7 +11885,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11869,7 +11933,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11878,18 +11942,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>374</v>
+        <v>383</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -11904,13 +11968,13 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>27</v>
@@ -11919,12 +11983,12 @@
         <v>36</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -11939,7 +12003,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11951,10 +12015,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11972,7 +12036,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11984,10 +12048,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12005,7 +12069,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12017,10 +12081,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12038,7 +12102,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12053,7 +12117,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12071,7 +12135,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12083,7 +12147,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>98</v>
@@ -12104,7 +12168,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12116,10 +12180,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12152,7 +12216,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12164,14 +12228,16 @@
         <v>34</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
-      <c r="M346" s="7"/>
+      <c t="s" r="M346" s="7">
+        <v>386</v>
+      </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
       <c t="s" r="A347" s="6">
@@ -12185,7 +12251,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12194,10 +12260,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>62</v>
@@ -12218,22 +12284,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12251,7 +12317,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12263,7 +12329,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c t="s" r="J349" s="7">
         <v>36</v>
@@ -12299,7 +12365,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12314,14 +12380,14 @@
         <v>38</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="K351" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -12336,7 +12402,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12351,7 +12417,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12369,7 +12435,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12381,10 +12447,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12417,7 +12483,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12426,18 +12492,18 @@
         <v>34</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c t="s" r="I355" s="7">
         <v>65</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -12452,13 +12518,13 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>34</v>
@@ -12467,7 +12533,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12485,7 +12551,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12494,13 +12560,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c t="s" r="I357" s="7">
         <v>63</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12518,22 +12584,22 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12566,7 +12632,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -12581,11 +12647,13 @@
         <v>77</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
-      <c r="M360" s="7"/>
+      <c t="s" r="M360" s="7">
+        <v>396</v>
+      </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
       <c t="s" r="A361" s="6">
@@ -12599,7 +12667,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -12611,7 +12679,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>23</v>
@@ -12632,7 +12700,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -12641,10 +12709,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>44</v>
@@ -12665,22 +12733,22 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>386</v>
+        <v>165</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12698,7 +12766,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -12713,7 +12781,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12731,7 +12799,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -12743,10 +12811,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12779,7 +12847,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12788,18 +12856,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c t="s" r="I367" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>390</v>
+        <v>400</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -12814,19 +12882,19 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>94</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>91</v>
@@ -12847,7 +12915,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12859,7 +12927,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>71</v>
@@ -12880,7 +12948,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12892,10 +12960,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12913,7 +12981,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12925,10 +12993,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12961,7 +13029,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -12976,12 +13044,12 @@
         <v>85</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>394</v>
+        <v>404</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -12996,7 +13064,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13011,7 +13079,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13021,15 +13089,15 @@
       <c t="s" r="A375" s="6">
         <v>13</v>
       </c>
-      <c r="B375" s="7">
-        <v>252</v>
+      <c t="s" r="B375" s="7">
+        <v>405</v>
       </c>
       <c t="s" r="C375" s="7">
         <v>14</v>
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -13038,64 +13106,72 @@
         <v>27</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>350</v>
+        <v>130</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>273</v>
-      </c>
-      <c r="K375" s="7"/>
+        <v>59</v>
+      </c>
+      <c t="s" r="K375" s="7">
+        <v>197</v>
+      </c>
       <c r="L375" s="7"/>
-      <c r="M375" s="7"/>
+      <c t="s" r="M375" s="7">
+        <v>406</v>
+      </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
       <c t="s" r="A376" s="6">
         <v>13</v>
       </c>
       <c r="B376" s="7">
-        <v>253</v>
+        <v>1383</v>
       </c>
       <c t="s" r="C376" s="7">
         <v>14</v>
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>126</v>
+        <v>406</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>386</v>
-      </c>
-      <c r="K376" s="7"/>
+        <v>336</v>
+      </c>
+      <c t="s" r="K376" s="7">
+        <v>44</v>
+      </c>
       <c r="L376" s="7"/>
-      <c r="M376" s="7"/>
+      <c t="s" r="M376" s="7">
+        <v>80</v>
+      </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
       <c t="s" r="A377" s="6">
         <v>13</v>
       </c>
       <c r="B377" s="7">
-        <v>216</v>
+        <v>282</v>
       </c>
       <c t="s" r="C377" s="7">
         <v>14</v>
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13104,13 +13180,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>179</v>
+        <v>41</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>395</v>
+        <v>110</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>195</v>
+        <v>363</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13121,29 +13197,29 @@
         <v>13</v>
       </c>
       <c r="B378" s="7">
-        <v>217</v>
+        <v>283</v>
       </c>
       <c t="s" r="C378" s="7">
         <v>14</v>
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>179</v>
+        <v>41</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>239</v>
+        <v>81</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13176,7 +13252,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13188,10 +13264,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13209,7 +13285,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13224,7 +13300,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13238,11 +13314,11 @@
         <v>8020</v>
       </c>
       <c t="s" r="C382" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13251,13 +13327,13 @@
         <v>94</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c t="s" r="I382" s="7">
         <v>82</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13271,26 +13347,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C383" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>94</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13323,7 +13399,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13332,17 +13408,19 @@
         <v>34</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
-      <c r="M385" s="7"/>
+      <c t="s" r="M385" s="7">
+        <v>412</v>
+      </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
       <c t="s" r="A386" s="6">
@@ -13356,13 +13434,13 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>34</v>
@@ -13371,7 +13449,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13389,7 +13467,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13404,7 +13482,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13437,7 +13515,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13452,7 +13530,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13470,7 +13548,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13503,7 +13581,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13512,16 +13590,16 @@
         <v>94</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c t="s" r="I391" s="7">
         <v>91</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c t="s" r="K391" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
@@ -13540,13 +13618,13 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>27</v>
@@ -13555,7 +13633,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="K392" s="7">
         <v>28</v>
@@ -13577,7 +13655,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13589,10 +13667,10 @@
         <v>90</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13610,7 +13688,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13622,10 +13700,10 @@
         <v>87</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13658,7 +13736,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13667,17 +13745,19 @@
         <v>34</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
-      <c r="M396" s="7"/>
+      <c t="s" r="M396" s="7">
+        <v>173</v>
+      </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
       <c t="s" r="A397" s="6">
@@ -13691,19 +13771,19 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c t="s" r="H397" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c t="s" r="J397" s="7">
         <v>110</v>
@@ -13724,7 +13804,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -13733,13 +13813,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13772,7 +13852,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -13781,10 +13861,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>22</v>
@@ -13792,7 +13872,7 @@
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -13807,26 +13887,28 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>42</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
-      <c r="M401" s="7"/>
+      <c t="s" r="M401" s="7">
+        <v>315</v>
+      </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
       <c t="s" r="A402" s="6">
@@ -13840,7 +13922,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -13855,7 +13937,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13873,7 +13955,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13885,7 +13967,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>161</v>
+        <v>406</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>115</v>
@@ -13906,7 +13988,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -13918,7 +14000,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>111</v>
@@ -13939,7 +14021,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -13987,7 +14069,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
@@ -13999,7 +14081,7 @@
         <v>90</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>19</v>
@@ -14007,7 +14089,7 @@
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14022,7 +14104,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -14034,7 +14116,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>53</v>
@@ -14042,7 +14124,7 @@
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>410</v>
+        <v>160</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14057,7 +14139,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
@@ -14066,17 +14148,21 @@
         <v>34</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c t="s" r="J409" s="7">
+        <v>123</v>
+      </c>
+      <c t="s" r="K409" s="7">
         <v>122</v>
       </c>
-      <c r="K409" s="7"/>
       <c r="L409" s="7"/>
-      <c r="M409" s="7"/>
+      <c t="s" r="M409" s="7">
+        <v>334</v>
+      </c>
     </row>
     <row r="410" ht="15" customHeight="1">
       <c t="s" r="A410" s="6">
@@ -14090,40 +14176,44 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>124</v>
-      </c>
-      <c r="K410" s="7"/>
+        <v>125</v>
+      </c>
+      <c t="s" r="K410" s="7">
+        <v>91</v>
+      </c>
       <c r="L410" s="7"/>
-      <c r="M410" s="7"/>
+      <c t="s" r="M410" s="7">
+        <v>422</v>
+      </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
       <c t="s" r="A411" s="6">
         <v>13</v>
       </c>
       <c r="B411" s="7">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c t="s" r="C411" s="7">
         <v>14</v>
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
@@ -14132,13 +14222,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>265</v>
+        <v>108</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>316</v>
+        <v>164</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14149,29 +14239,29 @@
         <v>13</v>
       </c>
       <c r="B412" s="7">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c t="s" r="C412" s="7">
         <v>14</v>
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>265</v>
+        <v>108</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>238</v>
+        <v>95</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14204,7 +14294,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -14219,7 +14309,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14252,13 +14342,13 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c t="s" r="H416" s="8">
         <v>90</v>
@@ -14267,14 +14357,14 @@
         <v>35</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c t="s" r="K416" s="7">
         <v>65</v>
       </c>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -14289,7 +14379,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -14298,7 +14388,7 @@
         <v>90</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c t="s" r="I417" s="7">
         <v>72</v>
@@ -14337,7 +14427,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
@@ -14346,7 +14436,7 @@
         <v>90</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c t="s" r="I419" s="7">
         <v>23</v>
@@ -14370,22 +14460,22 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>90</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14418,7 +14508,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
@@ -14427,13 +14517,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14451,19 +14541,19 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J423" s="7">
         <v>74</v>
@@ -14499,7 +14589,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="F425" s="7">
         <v>330</v>
@@ -14508,10 +14598,10 @@
         <v>94</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>24</v>
@@ -14519,7 +14609,7 @@
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>421</v>
+        <v>433</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -14534,22 +14624,22 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="F426" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>90</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14582,7 +14672,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="F428" s="7">
         <v>330</v>
@@ -14597,12 +14687,12 @@
         <v>75</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>424</v>
+        <v>436</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -14617,7 +14707,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="F429" s="7">
         <v>330</v>
@@ -14629,10 +14719,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14650,7 +14740,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
@@ -14659,13 +14749,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c t="s" r="I430" s="7">
         <v>63</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14673,7 +14763,7 @@
     </row>
     <row r="431" ht="15.75" customHeight="1">
       <c t="s" r="A431" s="9">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="B431" s="9"/>
       <c r="C431" s="9"/>
@@ -14693,7 +14783,7 @@
     <row r="432" ht="65.25" customHeight="1"/>
     <row r="433" ht="16.5" customHeight="1">
       <c t="s" r="A433" s="10">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="B433" s="10"/>
       <c r="C433" s="10"/>
@@ -14706,7 +14796,7 @@
       <c r="J433" s="10"/>
       <c r="K433" s="10"/>
       <c t="s" r="L433" s="11">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="M433" s="11"/>
       <c r="N433" s="11"/>
